--- a/23_03_2026.xlsx
+++ b/23_03_2026.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFC42D3-89B3-2446-8C10-8F5B11A480DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4686DE-9A4E-5C4B-AD4F-2F61D8D0AEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18280" yWindow="1420" windowWidth="15920" windowHeight="20720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooms" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="113">
   <si>
     <t>room_id</t>
   </si>
@@ -262,63 +262,6 @@
     <t>Monday</t>
   </si>
   <si>
-    <t>IPM Sec A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial Systems and Markets </t>
-  </si>
-  <si>
-    <t>IPM Sec B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indian Polity </t>
-  </si>
-  <si>
-    <t>MBA Sec C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Policy (ENVP) </t>
-  </si>
-  <si>
-    <t>TBA</t>
-  </si>
-  <si>
-    <t>MBA Sec E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supply Chain Management (SCM) </t>
-  </si>
-  <si>
-    <t>MBA Sec B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI in Marketing (AIMKT) </t>
-  </si>
-  <si>
-    <t>MBA Sec A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategic Marketing (SM) </t>
-  </si>
-  <si>
-    <t>MBA Sec D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Ethics (BEI&amp;W) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Communication-III </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Behavior </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Culture </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Leadership (BL) </t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -338,6 +281,81 @@
   </si>
   <si>
     <t>026</t>
+  </si>
+  <si>
+    <t>IPM04_A</t>
+  </si>
+  <si>
+    <t>Financial Systems and Markets</t>
+  </si>
+  <si>
+    <t>IPM04_B</t>
+  </si>
+  <si>
+    <t>Indian Polity</t>
+  </si>
+  <si>
+    <t>Digital Culture</t>
+  </si>
+  <si>
+    <t>Consumer Behavior</t>
+  </si>
+  <si>
+    <t>IPM05_A</t>
+  </si>
+  <si>
+    <t>Principles of Computational Thinking</t>
+  </si>
+  <si>
+    <t>IPM05_B</t>
+  </si>
+  <si>
+    <t>Critical Thinking and Problem Solving</t>
+  </si>
+  <si>
+    <t>Introduction to Psychology</t>
+  </si>
+  <si>
+    <t>MBA10_A</t>
+  </si>
+  <si>
+    <t>Strategic Marketing</t>
+  </si>
+  <si>
+    <t>MBA10_B</t>
+  </si>
+  <si>
+    <t>AI in Marketing</t>
+  </si>
+  <si>
+    <t>Pricing</t>
+  </si>
+  <si>
+    <t>Game Theory for Managers</t>
+  </si>
+  <si>
+    <t>Business Leadership</t>
+  </si>
+  <si>
+    <t>MBA10_C</t>
+  </si>
+  <si>
+    <t>ENVP</t>
+  </si>
+  <si>
+    <t>MBA10_D</t>
+  </si>
+  <si>
+    <t>MBA10_E</t>
+  </si>
+  <si>
+    <t>SCM</t>
+  </si>
+  <si>
+    <t>BEI&amp;W</t>
+  </si>
+  <si>
+    <t>BC-III</t>
   </si>
 </sst>
 </file>
@@ -392,13 +410,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,7 +788,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
@@ -789,8 +808,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>100</v>
+      <c r="A3" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -809,14 +828,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D4">
         <v>45</v>
@@ -829,14 +848,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>102</v>
+      <c r="A5" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -849,14 +868,14 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D6">
         <v>45</v>
@@ -869,8 +888,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>105</v>
+      <c r="A7" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -889,8 +908,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>106</v>
+      <c r="A8" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -909,7 +928,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B9" t="s">
@@ -929,7 +948,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B10" t="s">
@@ -949,7 +968,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B11" t="s">
@@ -969,7 +988,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B12" t="s">
@@ -989,7 +1008,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B13" t="s">
@@ -1009,7 +1028,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B14" t="s">
@@ -1029,7 +1048,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B15" t="s">
@@ -1049,7 +1068,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B16" t="s">
@@ -1069,7 +1088,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B17" t="s">
@@ -1089,7 +1108,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B18" t="s">
@@ -1109,7 +1128,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B19" t="s">
@@ -1129,7 +1148,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B20" t="s">
@@ -1149,7 +1168,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B21" t="s">
@@ -1169,7 +1188,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B22" t="s">
@@ -1189,7 +1208,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B23" t="s">
@@ -1209,7 +1228,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B24" t="s">
@@ -1229,7 +1248,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B25" t="s">
@@ -1256,16 +1275,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>74</v>
       </c>
@@ -1284,958 +1304,807 @@
       <c r="F1" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4">
+        <v>89</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="5">
         <v>0.375</v>
       </c>
       <c r="E2" s="4">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4">
+        <v>91</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="5">
         <v>0.375</v>
       </c>
       <c r="E3" s="4">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D4" s="4">
-        <v>0.39583333333333331</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="E4" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0.46875</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.46875</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.46875</v>
+      </c>
+      <c r="F12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.46875</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="F20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="F21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F22" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D25" s="5">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E25" s="5">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F25" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F26" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D27" s="5">
         <v>0.46875</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="E27" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="F27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="5">
         <v>0.46875</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E28" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="F28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="4">
-        <v>0.46875</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0.53125</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.46875</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0.53125</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0.53125</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0.53125</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="D29" s="5">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E29" s="5">
         <v>0.60416666666666663</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="F29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="5">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E30" s="5">
         <v>0.60416666666666663</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="3"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="3"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="3"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="3"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="3"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="3"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="3"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="3"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="3"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="3"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="3"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="3"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="3"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="3"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="3"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="3"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="3"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="3"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="3"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="3"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="3"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="3"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="3"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="3"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="3"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="3"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="3"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="3"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="3"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="3"/>
+      <c r="F30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G31" s="3"/>
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G52" s="3"/>
+    </row>
+    <row r="53" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G53" s="3"/>
+    </row>
+    <row r="54" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G54" s="3"/>
+    </row>
+    <row r="55" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G55" s="3"/>
+    </row>
+    <row r="56" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G57" s="3"/>
+    </row>
+    <row r="58" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G58" s="3"/>
+    </row>
+    <row r="59" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G59" s="3"/>
+    </row>
+    <row r="60" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G60" s="3"/>
+    </row>
+    <row r="61" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G61" s="3"/>
+    </row>
+    <row r="62" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G62" s="3"/>
+    </row>
+    <row r="63" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G63" s="3"/>
+    </row>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G65" s="3"/>
+    </row>
+    <row r="66" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G66" s="3"/>
+    </row>
+    <row r="67" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G67" s="3"/>
+    </row>
+    <row r="68" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G68" s="3"/>
+    </row>
+    <row r="69" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G69" s="3"/>
+    </row>
+    <row r="70" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G70" s="3"/>
+    </row>
+    <row r="71" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G71" s="3"/>
+    </row>
+    <row r="72" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G72" s="3"/>
+    </row>
+    <row r="73" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G73" s="3"/>
+    </row>
+    <row r="74" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G74" s="3"/>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G75" s="3"/>
+    </row>
+    <row r="76" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G76" s="3"/>
+    </row>
+    <row r="77" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G77" s="3"/>
+    </row>
+    <row r="78" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G78" s="3"/>
+    </row>
+    <row r="79" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G79" s="3"/>
+    </row>
+    <row r="80" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G80" s="3"/>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G81" s="3"/>
+    </row>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G82" s="3"/>
+    </row>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G83" s="3"/>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G84" s="3"/>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G85" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2245,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2262,7 +2131,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -2270,7 +2139,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>60</v>
@@ -2278,7 +2147,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -2286,7 +2155,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>75</v>
@@ -2294,7 +2163,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B6">
         <v>80</v>
@@ -2302,25 +2171,35 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10">
+        <v>80</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
@@ -2375,6 +2254,12 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
